--- a/从零开始学Slots/从零开始学Slots-25-基础篇-ExpandingWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-25-基础篇-ExpandingWild.xlsx
@@ -5741,6 +5741,9 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:N180" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -6198,5 +6201,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <ignoredErrors>
+    <ignoredError sqref="A1:T52" evalError="1" twoDigitTextYear="1" numberStoredAsText="1" formula="1" formulaRange="1" unlockedFormula="1" emptyCellReference="1" listDataValidation="1" calculatedColumn="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/从零开始学Slots/从零开始学Slots-25-基础篇-ExpandingWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-25-基础篇-ExpandingWild.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="179">
   <si>
     <r>
       <rPr>
@@ -4636,7 +4636,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4739,6 +4739,10 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5796,8 +5800,8 @@
       <c r="D4" s="13"/>
     </row>
     <row r="5" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="s">
-        <v>128</v>
+      <c r="A5" s="26">
+        <v>1</v>
       </c>
       <c r="B5" s="14" t="s">
         <v>129</v>
@@ -5809,8 +5813,8 @@
       <c r="E5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="s">
-        <v>131</v>
+      <c r="A6" s="26">
+        <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>132</v>
@@ -5822,8 +5826,8 @@
       <c r="E6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="14" t="s">
-        <v>134</v>
+      <c r="A7" s="26">
+        <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>135</v>
@@ -5836,8 +5840,8 @@
       <c r="F7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="16" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="14" t="s">
-        <v>137</v>
+      <c r="A8" s="26">
+        <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>138</v>
@@ -5851,8 +5855,8 @@
       <c r="G8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="14" t="s">
-        <v>140</v>
+      <c r="A9" s="26">
+        <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>141</v>

--- a/从零开始学Slots/从零开始学Slots-25-基础篇-ExpandingWild.xlsx
+++ b/从零开始学Slots/从零开始学Slots-25-基础篇-ExpandingWild.xlsx
@@ -4462,11 +4462,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00%"/>
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.0000000000%"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -4636,7 +4637,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -4742,6 +4743,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6000,7 +6009,7 @@
       <c r="D20" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="28" t="n">
         <f aca="false">B20*C20*D20</f>
         <v>0.008</v>
       </c>
@@ -6026,7 +6035,7 @@
       <c r="D21" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="E21" s="17" t="n">
+      <c r="E21" s="28" t="n">
         <f aca="false">B21*C21*D21</f>
         <v>0.04</v>
       </c>
@@ -6052,7 +6061,7 @@
       <c r="D22" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="E22" s="17" t="n">
+      <c r="E22" s="28" t="n">
         <f aca="false">B22*C22*D22</f>
         <v>0.2</v>
       </c>
@@ -6078,7 +6087,7 @@
       <c r="D23" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="17" t="n">
+      <c r="E23" s="28" t="n">
         <f aca="false">B23*C23*D23</f>
         <v>1</v>
       </c>
